--- a/MAJSushiConfig/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/ConceptMap/FRMedicationAdministrationLMCDAFHIR</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/ConceptMap/FRMedicationAdministrationLMCDAFHIR</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationAdministration</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationAdministration|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -159,7 +159,7 @@
     <t>FRLMMedicationAdministration.note</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDosageInstructions</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDosageInstructions|0.1.0</t>
   </si>
   <si>
     <t>FRLMDosageInstructions.renderedDosageInstruction</t>

--- a/MAJSushiConfig/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
